--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -3360,7 +3360,7 @@
     <t>625</t>
   </si>
   <si>
-    <t>Orthoptie : orientation troubles neuro-visuels (pathologies neurologiques, maladies neurodégénératives)</t>
+    <t>Orthoptie orientation neurovisuelle adulte (pathologies neurologiques, maladies neurodégénératives)</t>
   </si>
   <si>
     <t>626</t>
